--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_03_17_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_03_17_Cau.xlsx
@@ -679,7 +679,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn những yếu tố giúp kiểm tra mục tiêu trước và sau lần chạy.</t>
+          <t>Một ngưỡng chất lượng cam kết trước (pre-committed quality gate) hợp lệ bắt buộc phải có: (a) Ngưỡng định lượng bằng số; (b) Điều kiện bắt buộc (hard constraints/fatal gates) đối với rủi ro nghiêm trọng; (c) Mốc thời gian và phiên bản đóng băng trước khi chạy đánh giá đầy đủ; (e) Mục tiêu so sánh chuẩn (baseline benchmark) được cố định trước. Không được phép hạ ngưỡng sau khi thấy kết quả (harking/p-hacking) hay tuyên bố giả tạo.</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người chấm phải có thể tính lại được kết quả.</t>
+          <t>Hồ sơ ghi lại một lần chạy đánh giá (evaluation run profile) hoàn chỉnh và có thể tái lập (reproducible) phải lưu trữ đầy đủ: toàn bộ dữ liệu vào và kết quả của từng tình huống kiểm thử, điểm đánh giá chi tiết theo từng khía cạnh, các số liệu tổng hợp, mốc phiên bản/ngưỡng chất lượng đã cam kết, và danh sách toàn bộ các tình huống thất bại.</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Con số chỉ có nghĩa khi đặt cạnh ngưỡng đã cam kết trước.</t>
+          <t>Khi kết quả thực tế chỉ đạt 76% so với ngưỡng cam kết trước 85%, cách sửa đổi trung thực và đúng chuẩn khoa học là công bố rõ ràng kết quả 76% chưa đạt ngưỡng cam kết 85%, đồng thời phân tích cụ thể các nhóm lỗi chính và đề xuất thử nghiệm cải tiến tiếp theo; không được ngụy tạo hay dịch chuyển cột mốc chất lượng.</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ dấu vết và minh bạch về phần chạy trực tiếp/bản dự phòng.</t>
+          <t>Khi giám khảo hoặc người dùng đưa dữ liệu đầu vào lạ tại chỗ trong buổi demo trực tiếp: (a) Chạy dữ liệu qua bản mẫu hiện có; (b) Giữ đúng cam kết về hành vi và xử lý lỗi đã công bố; (c) Nếu phải chuyển sang dùng bản dự phòng thì phải thông báo minh bạch; (e) Nếu hệ thống không đạt, thẳng thắn chỉ ra hành vi quan sát được thay vì che giấu. Tuyệt đối không âm thầm sửa prompt tại chỗ.</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt tài liệu dự phòng với trạng thái lần chạy hiện tại.</t>
+          <t>Khi buổi demo trực tiếp gặp sự cố hết thời gian chờ (timeout) và phải chuyển sang sử dụng video ghi sẵn (fallback video), nhóm trình bày có thể dùng bản ghi dự phòng nhưng bắt buộc phải nêu rõ lần chạy trực tiếp không đạt và đây là video dự phòng; việc tuyên bố hệ thống vừa chạy thành công trực tiếp là vi phạm tính trung thực khoa học.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_03_17_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_03_17_Cau.xlsx
@@ -624,10 +624,27 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ ngưỡng và lịch sử; lập phiên bản cho phần định nghĩa bị lỗi.
-Phân tích theo nguyên lý thiết kế: Giữ ngưỡng và lịch sử; lập phiên bản cho phần định nghĩa bị lỗi.</t>
+- 1.0 điểm: Phân biệt chính xác giữa việc mô hình yếu kém thực tế và sai lệch đo lường do tiêu chí exact match.
+- 1.0 điểm: Giữ nguyên ngưỡng cam kết chất lượng ban đầu (80%), không tự tiện hạ thấp chuẩn mực.
+- 1.0 điểm: Quy định lưu giữ nguyên vẹn lịch sử lần chạy ban đầu, không được xóa dấu vết.
+- 1.0 điểm: Đề xuất lập phiên bản tiêu chí (Metric versioning v1 -&gt; v2) và báo cáo đối chiếu song song minh bạch.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân biệt Rạch ròi giữa 'Không đạt Ngưỡng' và 'Lỗi Tiêu chí Đánh giá':
+- Không đạt Ngưỡng (Genuine Performance Failure below Quality Bar):
+  + Định nghĩa: Xảy ra khi mô hình thực sự tạo ra các câu trả lời sai lệch về mặt bản chất tri thức, có lỗi ảo giác hoặc vi phạm thẩm quyền, khiến tỷ lệ câu trả lời chuẩn xác thực tế thấp hơn ngưỡng cam kết 80%.
+- Lỗi Tiêu chí Đánh giá (Flawed Evaluation Metric / Measurement Artifact):
+  + Định nghĩa: Xảy ra khi công cụ đo lường hoặc định nghĩa tiêu chí chấm điểm bị sai lệch về mặt phương pháp luận (như tiêu chí 'giống câu chữ chính xác' - Exact String Matching). Trong trường hợp này, các câu trả lời của mô hình hoàn toàn đúng về mặt ngữ nghĩa và sự kiện, nhưng bị máy chấm đánh trượt oan do diễn đạt bằng từ đồng nghĩa.
+2. Hồ sơ Bắt buộc phải Lưu giữ (Evaluation Governance Records):
+- Lưu giữ vẹn nguyên Lịch sử Lần chạy đầu tiên (Immutable Run Record v1):
+  + Giữ nguyên toàn bộ log của lần chạy ban đầu với tiêu chí cũ (ghi nhận tỷ lệ pass thấp do lỗi exact match), tuyệt đối không xóa bỏ hay sửa đè số liệu lịch sử.
+- Ban hành Phiên bản mới cho Tiêu chí Đánh giá (Metric Versioning):
+  + Tạo tài liệu thay đổi tiêu chuẩn: `eval_rubric_v2` thay thế tiêu chí Exact Match bằng Semantic Equivalence.
+- Báo cáo đối chiếu song song (Dual-Metric Benchmark Report):
+  + Trình bày báo cáo minh bạch gồm 2 cột: Kết quả theo tiêu chí cũ (đánh dấu lỗi phương pháp) và Kết quả sau khi áp dụng tiêu chí đã sửa chữa v2 trên cùng một bộ phản hồi của mô hình.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quality Bar Precommitment đòi hỏi sự trung thực tuyệt đối trong đo lường AI. Khi phát hiện tiêu chí đo lường bị lỗi, đội ngũ không được âm thầm hạ thấp ngưỡng cam kết chất lượng (80%) mà phải lập phiên bản mới cho tiêu chí đánh giá, đồng thời lưu giữ đầy đủ dấu vết lịch sử để phục vụ kiểm toán độc lập.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST AI Evaluation Standards &amp; Software Quality Engineering Audit Traceability Principles (https://www.nist.gov/itl/ai-risk-management-framework)</t>
         </is>
       </c>
     </row>
@@ -710,10 +727,27 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đạt tỷ lệ phần trăm chưa đủ nếu điều kiện bắt buộc bị vi phạm.
-Phân tích theo nguyên lý thiết kế: Đạt tỷ lệ phần trăm chưa đủ nếu điều kiện bắt buộc bị vi phạm.</t>
+- 1.0 điểm: Tính toán đúng tỷ lệ đạt trên toàn bộ 20 ca (16/20 = 80%).
+- 1.0 điểm: Đưa ra kết luận chính xác: Lần chạy KHÔNG ĐẠT (Fail) do vi phạm điều kiện cấm về thẩm quyền.
+- 1.0 điểm: Khẳng định nguyên tắc an toàn: tỷ lệ 80% không có giá trị khi điều kiện bắt buộc (zero authority violation) bị vi phạm.
+- 1.0 điểm: Chỉ ra dứt khoát lỗi vi phạm liêm chính hồ sơ: hành vi xóa bỏ dữ liệu thất bại là sai phạm kiểm toán nghiêm trọng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán lại và Kết luận Đúng đắn về Lần Chạy Đánh giá:
+- Mẫu số chuẩn hợp lệ: 20 tình huống (Bộ mẫu chuẩn ban đầu).
+- Số tình huống đạt thực tế: 16 tình huống.
+- Tỷ lệ đạt thực tế = `16 / 20 = 80,0%` (Vừa chạm đúng ngưỡng tối thiểu 80%).
+- Số vi phạm thẩm quyền: Có đúng 1 tình huống vi phạm thẩm quyền trong số 4 ca không đạt bị che giấu.
+- KẾT LUẬN CUỐI CÙNG: LẦN CHẠY BỊ ĐÁNH GIÁ LÀ KHÔNG ĐẠT (FAIL / REJECTED).
+- Biện minh: Ngưỡng cam kết chất lượng quy định rõ điều kiện kép: 'Ít nhất 80% VÀ KHÔNG CÓ VI PHẠM VỀ THẨM QUYỀN'. Mặc dù tỷ lệ phần trăm số học đạt 80%, nhưng hệ thống đã phạm phải 1 lỗi vi phạm thẩm quyền (Zero-Tolerance Security Constraint). Do đó, lần chạy này hoàn toàn không đủ điều kiện phát hành.
+2. Chỉ ra các Lỗi Nghiêm trọng trong Hồ sơ (Audit Integrity Violations):
+- Lỗi Giả mạo và Che giấu Dữ liệu Kiểm toán (Data Tampering / Hiding Failed Cases):
+  + Việc tự ý xóa 4 tình huống không đạt khỏi bảng kết quả là hành vi gian lận dữ liệu kiểm thử nghiêm trọng (Scientific Fraud), làm sai lệch hoàn toàn bức tranh chất lượng của hệ thống.
+- Lỗi Che giấu Rủi ro An ninh Cao nhất:
+  + Việc xóa tình huống vi phạm thẩm quyền là hành vi cố tình che giấu lỗ hổng an toàn nghiêm trọng, đẩy sản phẩm vào nguy cơ rủi ro pháp lý khi triển khai thực tế.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong đánh giá chất lượng sản phẩm AI, 'Tỷ lệ phần trăm đạt' không bao giờ có thể bù đắp cho các vi phạm an toàn cấm tuyệt đối (Zero-tolerance Authority Violations). Hành vi xóa bỏ các ca không đạt khỏi hồ sơ kiểm thử vi phạm nghiêm trọng liêm chính kỹ thuật và sẽ bị các kiểm toán viên an ninh phế truất ngay lập tức.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Teamwork Integrity Mandate - Zero Tolerance for Facade Reporting &amp; AI Safety Evaluation Benchmarks (https://www.nist.gov/itl/ai-risk-management-framework)</t>
         </is>
       </c>
     </row>
@@ -790,10 +824,27 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một thay đổi prompt tạo ra một lần đo mới.
-Phân tích theo nguyên lý thiết kế: Một thay đổi prompt tạo ra một lần đo mới.</t>
+- 1.0 điểm: Khẳng định nguyên tắc: sửa prompt tạo ra lần chạy mới, tuyệt đối không ghi đè dữ liệu cũ.
+- 1.0 điểm: Thiết lập cấu trúc hồ sơ chuẩn hóa tách thành 2 bản ghi độc lập có Run ID và Prompt Version riêng biệt.
+- 1.0 điểm: Bảo toàn toàn bộ câu trả lời cũ và câu trả lời mới song song trong cơ sở dữ liệu kiểm thử.
+- 1.0 điểm: Bổ sung đầy đủ metadata kiểm toán (mã băm prompt SHA-256, timestamp, lý do thay đổi).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Sửa đổi Dấu vết Nguồn gốc của Hồ sơ Lần chạy (Fixing Eval Run Traceability &amp; Data Lineage):
+1. Nguyên tắc Cốt lõi: Một thay đổi Prompt tạo ra một Phiên đánh giá hoàn toàn mới (New Evaluation Run Instance). Tuyệt đối không bao giờ được ghi đè kết quả của lần chạy mới lên cùng một dòng dữ liệu của lần chạy cũ.
+2. Cấu trúc Hồ sơ Lần chạy Chuẩn hóa sau khi sửa đổi:
+Tách thành 2 bản ghi riêng biệt với khóa phức hợp gồm `(run_id, test_case_id, prompt_version)`:
+| Run ID | Prompt Version | Case ID | Trạng thái | Câu trả lời thực tế lưu vết | Mã băm Prompt | Thời điểm ghi nhận |
+| :--- | :--- | :--- | :---: | :--- | :--- | :--- |
+| `RUN_20261023_01` | `prompt_v1.0` | `TC-042` | **FAIL** | "Câu trả lời cũ bị lỗi của model..." | `sha256:abc123...` | `2026-10-23 09:15:00` |
+| `RUN_20261023_02` | `prompt_v1.1` | `TC-042` | **PASS** | "Câu trả lời mới đã sửa chuẩn xác..." | `sha256:def456...` | `2026-10-23 14:30:00` |
+3. Các thông tin Bắt buộc phải khôi phục và bảo toàn:
+- Khôi phục lại nội dung câu trả lời cũ của lần chạy 1 từ nhật ký lưu trữ thô (raw telemetry logs).
+- Lưu vết mã commit Git hoặc SHA-256 tương ứng của từng phiên bản prompt.
+- Bổ sung trường `change_rationale`: Ghi rõ prompt v1.1 đã sửa đổi mệnh đề nào dẫn đến việc chuyển trạng thái từ FAIL sang PASS trên ca `TC-042`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong MLOps/LLMOps, tính bất biến của dữ liệu kiểm thử (Immutability of Eval Records) là yêu cầu tiên quyết. Ghi đè kết quả cũ làm phá hủy đường truyền nguồn gốc (Data Lineage), khiến đội ngũ không thể so sánh A/B test, không thể kiểm tra lỗi hồi quy và làm mất tính minh bạch khoa học của toàn bộ dự án.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+MLOps Data Lineage Best Practices (DVC / MLflow) &amp; ISO/IEC 25010 Software Quality Standards (https://dvc.org/doc/user-guide/data-management)</t>
         </is>
       </c>
     </row>
@@ -824,10 +875,25 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Quan sát điều người tham gia làm, không giải thích hộ họ.
-Phân tích theo nguyên lý thiết kế: Quan sát điều người tham gia làm, không giải thích hộ họ.</t>
+- 1.0 điểm: Soạn thảo lời giao nhiệm vụ tự nhiên, khách quan, không mớm ý giải pháp.
+- 1.0 điểm: Nêu rõ 2 điều cấm của người điều phối: không chỉ dẫn thao tác và không giải thích/biện minh cho hệ thống.
+- 1.0 điểm: Liệt kê đủ 3 loại quan sát hành vi khách quan (điểm do dự, đường đi thao tác, biểu cảm phi ngôn ngữ).
+- 1.0 điểm: Khẳng định nguyên tắc ghi nhận hành vi thực tế trước khi hỏi phỏng vấn ý kiến cá nhân.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Phiên Quan sát Nhiệm vụ Im lặng (10-minute Silent Task Observation Session):
+1. Hướng dẫn Giao nhiệm vụ cho Người tham gia (Task Briefing):
+"Chào bạn! Cảm ơn bạn đã tham gia buổi trải nghiệm hôm nay. Trước mặt bạn là bản mẫu của tính năng tìm kiếm bài giảng. Nhiệm vụ của bạn trong 10 phút tới là: Hãy tìm lại chính xác phân đoạn video bài giảng tuần trước có giải thích về 'công thức tính Attention Weight' và mở đúng đoạn đó lên màn hình. Bạn hãy thao tác hoàn toàn tự nhiên như khi đang tự học ở nhà. Trong suốt quá trình này, mình sẽ chỉ ngồi quan sát và ghi chép, bạn cứ thoải mái tương tác nhé!"
+2. Hai Điều Người điều phối TUYỆT ĐỐI KHÔNG ĐƯỢC LÀM (Facilitator Prohibitions):
+- Điều cấm 1: Tuyệt đối KHÔNG giải thích hộ hoặc hướng dẫn cách làm khi sinh viên bị lúng túng (ví dụ: không được nói 'bạn bấm vào thanh tìm kiếm bên trái kìa' hay 'hãy gõ từ khóa X').
+- Điều cấm 2: Tuyệt đối KHÔNG biện minh hay giải thích lý do thiết kế khi hệ thống bị chậm hoặc sinh viên gặp lỗi (ví dụ: không được nói 'chỗ này do AI đang gọi API nên hơi lag' hoặc 'giao diện này nhóm chưa kịp làm nút quay lại').
+3. Ba Loại Quan sát Hành vi BẮT BUỘC PHẢI GHI NHẬN trước khi hỏi ý kiến:
+- Quan sát 1 (Điểm do dự / Tắc nghẽn hành vi - Hesitation &amp; Friction Points): Ghi nhận vị trí con trỏ chuột dừng lại lâu (&gt;5 giây), nơi sinh viên click nhầm nhiều lần hoặc đọc đi đọc lại câu chữ mà không thao tác tiếp.
+- Quan sát 2 (Đường đi thao tác thực tế - Navigation Path &amp; Workarounds): Ghi nhận trình tự các bước sinh viên đã bấm, các từ khóa cụ thể mà sinh viên đã gõ vào ô tìm kiếm.
+- Quan sát 3 (Biểu cảm và Phản ứng phi ngôn ngữ - Non-verbal Reactions): Ghi nhận tiếng thở dài, nhíu mày, lắc đầu hoặc nụ cười khi tìm thấy kết quả.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phương pháp Silent Task Observation (quan sát nhiệm vụ trong im lặng) triệt tiêu hoàn toàn hiệu ứng người quan sát (Hawthorne Effect) và thiên kiến dẫn dắt. Người làm sản phẩm phải ghi nhận hành vi chân thực của người dùng trước, bởi vì những gì người dùng làm (Actions) luôn phản ánh sự thật khách quan hơn nhiều so với những gì họ nói (Opinions).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Steve Krug - Don't Make Me Think (Usability Testing Guide) &amp; Jakob Nielsen - Usability Engineering (https://sensible.com/dont-make-me-think/)</t>
         </is>
       </c>
     </row>
@@ -858,10 +924,29 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không hỏi 'bạn có thích/tính năng này có hữu ích không?'.
-Phân tích theo nguyên lý thiết kế: Không hỏi 'bạn có thích/tính năng này có hữu ích không?'.</t>
+- 1.0 điểm: Câu hỏi 1 đo điểm khó chịu trung lập, không mớm lời, tập trung vào khoảnh khắc bị khựng lại.
+- 1.0 điểm: Câu hỏi 2 đo niềm tin có lý do, đào sâu căn cứ khiến người dùng tin hoặc nghi ngờ kết quả.
+- 1.0 điểm: Câu hỏi 3 đo ý định sử dụng thông qua khám phá rào cản ngăn cản thực tế thay vì hỏi sở thích chung chung.
+- 1.0 điểm: Nêu rõ thông tin kèm theo cần giữ (nguyên văn trích dẫn, trạng thái hoàn thành thực tế, user ID).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Soạn thảo Ba Câu hỏi Phỏng vấn Trung lập Sau Nhiệm vụ (Post-Task Validation Probing):
+1. Câu hỏi 1: Đo lường Điểm khó chịu / Khó hiểu (Friction &amp; Cognitive Confusion Probe):
+- Câu hỏi: "Trong suốt quá trình tìm kiếm đoạn bài giảng vừa rồi, có bước nào hoặc khoảnh khắc nào khiến bạn cảm thấy bị khựng lại, khó hiểu, hoặc không diễn ra như bạn kỳ vọng không?"
+- Mục đích: Bộc lộ các điểm nghẽn trải nghiệm mà không gán nhãn tiêu cực hay phòng thủ.
+2. Câu hỏi 2: Đo lường Mức độ Tin tưởng có Lý do (Calibrated Trust Probe):
+- Câu hỏi: "Khi trợ giảng AI hiển thị phân đoạn bài giảng này, điều gì đã khiến bạn quyết định tin tưởng (hoặc nghi ngờ) rằng đây chính là đoạn video giảng về công thức Attention mà bạn cần?"
+- Mục đích: Đo lường xem niềm tin của người dùng dựa trên bằng chứng minh bạch (như trích dẫn, tiêu đề, thời lượng) hay chỉ là phỏng đoán cảm tính.
+3. Câu hỏi 3: Đo lường Ý định Sử dụng có Rào cản (Usage Intent with Friction Trade-off):
+- Câu hỏi: "Trong đợt ôn thi môn học sắp tới, điều gì cụ thể có thể ngăn cản bạn hoặc khiến bạn ngần ngại không sử dụng công cụ này để tìm lại bài học?"
+- Mục đích: Khám phá các rào cản thực tế (như sợ chậm, sợ phụ thuộc, rào cản thiết bị) thay vì nhận những lời khen xã giao vô nghĩa.
+4. Thông tin Kèm theo Bắt buộc phải Lưu giữ (Contextual Metadata):
+- Trích dẫn nguyên văn (Verbatim Quotes) kèm dấu thời gian video quay phiên phỏng vấn.
+- Trạng thái hoàn thành nhiệm vụ thực tế của người tham gia (Đạt hay Không đạt nhiệm vụ).
+- Định danh người tham gia (P1, P2...) và mức độ am hiểu công nghệ/môn học ban đầu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sau buổi thử nghiệm, các câu hỏi định hướng như 'Bạn có thích tính năng này không?' hoàn toàn vô giá trị vì người dùng thường có xu hướng trả lời lịch sự làm hài lòng người phỏng vấn (Social Desirability Bias). Các câu hỏi trung lập tập trung vào rào cản, lý do tin tưởng và sự việc cụ thể sẽ mang lại dữ liệu cải tiến đắt giá.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Rob Fitzpatrick - The Mom Test: How to Talk to Customers When Everyone Is Lying to You (https://www.momtestbook.com/)</t>
         </is>
       </c>
     </row>
@@ -892,10 +977,25 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chủ đề lặp lại và có hậu quả cao đứng trước sở thích đơn lẻ.
-Phân tích theo nguyên lý thiết kế: Chủ đề lặp lại và có hậu quả cao đứng trước sở thích đơn lẻ.</t>
+- 1.0 điểm: Đưa ra Quyết định Thay đổi chính xác (bổ sung liên kết nguồn) có truy vết tới P1, P2, P4 với mức nghiêm trọng cao.
+- 1.0 điểm: Đưa ra Quyết định Giữ nguyên chính xác (giữ cấu trúc chi tiết) có lập luận về việc P5 vẫn hoàn thành nhiệm vụ tốt.
+- 1.0 điểm: Đưa ra Quyết định Để sau chính xác (Dark mode của P3) có lập luận về sở thích đơn lẻ, mức nghiêm trọng thấp.
+- 1.0 điểm: Thể hiện tư duy quản trị ưu tiên theo bằng chứng thực nghiệm (Evidence-driven Triage).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Đưa ra Ba Quyết định Sản phẩm có Dấu vết từ Kết quả Thử nghiệm (Traceable Product Decisions):
+1. Quyết định THAY ĐỔI (Change Decision - Ưu tiên Cao nhất):
+- Nội dung quyết định: Bổ sung liên kết nguồn trích dẫn trực tiếp (Source Link / Timestamp Link) hiển thị nổi bật ngay bên cạnh mỗi câu trả lời của trợ giảng AI.
+- Dấu vết bằng chứng thực nghiệm: Vấn đề này xuất hiện lặp lại ở 3 trên 5 người kiểm thử (P1, P2, P4 đều không thấy liên kết nguồn) và được đánh giá ở mức độ nghiêm trọng cao (High Severity). Việc thiếu liên kết nguồn khiến người học không thể xác minh tính đúng đắn của câu trả lời, làm phá vỡ giá trị cốt lõi của sản phẩm học tập.
+2. Quyết định GIỮ NGUYÊN (Keep As-Is Decision):
+- Nội dung quyết định: Giữ nguyên cấu trúc nội dung chi tiết hiện tại của câu trả lời, không cắt tỉa quá ngắn.
+- Dấu vết bằng chứng thực nghiệm: Người kiểm thử P5 nhận xét câu trả lời có hơi dài (mức độ nghiêm trọng trung bình), nhưng dữ liệu quan sát thực tế cho thấy P5 vẫn hoàn thành nhiệm vụ thành công 100% và nắm vững kiến thức. Việc cắt ngắn quá mức câu trả lời có nguy cơ làm mất các bước diễn giải sư phạm quan trọng cho đa số sinh viên khác.
+3. Quyết định ĐỂ SAU (Defer to Backlog Decision):
+- Nội dung quyết định: Đưa yêu cầu phát triển giao diện nền tối (Dark Mode) vào danh sách việc để sau (Product Backlog), chưa xem xét triển khai trong vòng 3 sprint tới.
+- Dấu vết bằng chứng thực nghiệm: Đây là yêu cầu sở thích giao diện mang tính cá nhân đơn lẻ của duy nhất 1 người dùng (P3) với mức độ nghiêm trọng rất thấp (Low Severity), hoàn toàn không ảnh hưởng đến khả năng hoàn thành nhiệm vụ tìm kiếm và học tập của sinh viên.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quản trị sản phẩm AI đòi hỏi kỷ luật ưu tiên dựa trên mức độ nghiêm trọng và tần suất xuất hiện của bằng chứng. Một vấn đề lặp lại ở 3/5 người (P1, P2, P4) có tính sinh tử (thiếu liên kết nguồn) phải được thực thi thay đổi ngay lập tức, trong khi sở thích thẩm mỹ cá nhân đơn lẻ (P3 đòi Dark mode) phải bị đẩy lùi vào backlog.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Marty Cagan - Inspired: How to Create Tech Products Customers Love &amp; UX Issue Severity Rating Framework (https://www.svpg.com/books/inspired-how-to-create-tech-products-customers-love/)</t>
         </is>
       </c>
     </row>
@@ -1026,10 +1126,36 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 6 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi phần trả lời 'tuyên bố này được kiểm bằng tài liệu nào?'.
-Phân tích theo nguyên lý thiết kế: Mỗi phần trả lời 'tuyên bố này được kiểm bằng tài liệu nào?'.</t>
+- 1.0 điểm: Phần 1 (Vấn đề) gắn chính xác với bằng chứng số lượng định lượng 41/200.
+- 1.0 điểm: Phần 2 (Tác động) gắn chính xác với Bảng tác động (Impact Matrix).
+- 1.0 điểm: Phần 3 (Trình diễn) gắn chính xác với Bản mẫu tương tác (Working Prototype).
+- 1.0 điểm: Phần 4 (Năng lực) công bố trung thực kết quả lần chạy 76% so với ngưỡng 85%.
+- 1.0 điểm: Phần 5 (Người dùng) gắn chính xác với trích dẫn nguyên văn của P2 ('không thấy nguồn').
+- 1.0 điểm: Phần 6 (Cải tiến) gắn chính xác với Nhật ký thay đổi (Changelog) đã bổ sung liên kết nguồn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Dàn ý Sáu Phần Trình diễn Sản phẩm (Evidence-Backed Demo Script with Claim-Evidence Traceability):
+1. Phần 1: Tuyên bố Vấn đề Thực tế (Real Problem Claim)
+- Tuyên bố của nhóm: "Sinh viên gặp điểm nghẽn nghiêm trọng khi tìm kiếm lại các đoạn video bài giảng để ôn tập, dẫn đến lãng phí thời gian và bỏ dở bài tập."
+- Dấu vết bằng chứng tương ứng: Báo cáo khảo sát định lượng với số liệu thực tế **41 / 200** sinh viên phản ánh gặp tình trạng này trong khảo sát nhu cầu ban đầu.
+2. Phần 2: Giải pháp Sản phẩm và Tác động Dự kiến (Product Solution &amp; Impact Claim)
+- Tuyên bố của nhóm: "Tính năng Trợ giảng AI tìm kiếm bài giảng theo ngữ nghĩa giúp rút ngắn 70% thời gian định vị kiến thức cho sinh viên và giảm tải áp lực hỗ trợ cho giảng viên."
+- Dấu vết bằng chứng tương ứng: **Bảng phân tích tác động giá trị (Impact Matrix)** kết hợp với Mô hình tính toán ROI tiết kiệm thời gian học tập.
+3. Phần 3: Trình diễn Trải nghiệm Thực tế (Live Product Experience Claim)
+- Tuyên bố của nhóm: "Hệ thống có luồng người dùng khép kín, hoạt động ổn định từ lúc nhập câu hỏi tìm kiếm đến khi mở chính xác video bài giảng."
+- Dấu vết bằng chứng tương ứng: **Bản mẫu hoạt động thực tế (Interactive Working Prototype)** kết nối trực tiếp với cơ sở dữ liệu video bài giảng.
+4. Phần 4: Đánh giá Năng lực Kỹ thuật Trung thực (Honest Technical Benchmark Claim)
+- Tuyên bố của nhóm: "Trong lần chạy đánh giá năng lực gần nhất, hệ thống đạt độ chính xác 76%, hiện chưa đạt ngưỡng cam kết chất lượng 85% và nhóm đã xác định rõ các lỗi cần cải tiến."
+- Dấu vết bằng chứng tương ứng: **Biên bản kết quả kiểm thử đánh giá kỹ thuật (Eval Run Report: 76% vs 85% Target)** được công bố trung thực, không giấu giếm.
+5. Phần 5: Tiếng nói Người dùng Thực tế (User Discovery Feedback Claim)
+- Tuyên bố của nhóm: "Thử nghiệm người dùng thực tế chỉ ra rằng việc hiển thị câu trả lời mà thiếu liên kết đối chiếu nguồn gốc là rào cản lớn nhất đối với niềm tin của người học."
+- Dấu vết bằng chứng tương ứng: **Trích dẫn nguyên văn của người dùng kiểm thử P2: 'tôi không thấy liên kết nguồn đâu cả'** trích xuất từ video phiên thử nghiệm khả dụng.
+6. Phần 6: Vòng lặp Cải tiến Khép kín (Continuous Improvement Trace Claim)
+- Tuyên bố của nhóm: "Đội ngũ đã lập tức phản hồi tiếng nói người dùng và cập nhật thành công tính năng trích dẫn nguồn trên phiên bản mới nhất."
+- Dấu vết bằng chứng tương ứng: **Nhật ký thay đổi mã nguồn (Git Changelog)** và giao diện mới đã được cập nhật nút liên kết nguồn trực tiếp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một bài thuyết trình sản phẩm AI đẳng cấp (Evidence-Backed Demo) không dựa vào những lời hoa mỹ sáo rỗng mà dựa trên tính liên kết chặt chẽ giữa Tuyên bố (Claim) và Bằng chứng (Evidence). Việc công khai trung thực cả những số liệu chưa đạt (76% vs 85%) và trích dẫn phản hồi chê của người dùng (P2) chính là minh chứng cao nhất cho năng lực quản lý dự án chuyên nghiệp và đáng tin cậy.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Alberto Savoia - Pretotyping &amp; Pitching with Evidence &amp; Stanford d.school - Storytelling with Data and Prototypes (https://www.pretotyping.org/)</t>
         </is>
       </c>
     </row>
@@ -1154,10 +1280,25 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nêu hệ thống làm gì khi thành công và khi điều kiện khó xuất hiện.
-Phân tích theo nguyên lý thiết kế: Nêu hệ thống làm gì khi thành công và khi điều kiện khó xuất hiện.</t>
+- 1.0 điểm: Thiết kế Tình huống chuẩn đầy đủ câu hỏi, câu trả lời và trích dẫn video kèm timestamp.
+- 1.0 điểm: Thiết kế Tình huống khó gài đúng các rủi ro thẩm quyền và yêu cầu ngoài nguồn dữ liệu.
+- 1.0 điểm: Hệ thống xử lý tình huống khó xuất sắc: từ chối vi phạm thẩm quyền lịch sự, không lỗi hệ thống.
+- 1.0 điểm: Nêu rõ cam kết hành vi minh bạch trước tình huống lạ của giám khảo (chân thực nguồn, không ảo giác).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Kịch bản Trình diễn Trực tiếp (Live Demo Standard &amp; Hard Case Design):
+1. Tình huống Chuẩn (Standard / Golden Case):
+- Đầu vào: 'Khái niệm Multi-Head Attention được giải thích ở bài học nào?'
+- Hành vi hệ thống kỳ vọng: Trợ giảng AI xử lý trong 2 giây, trả lời súc tích khái niệm Multi-Head Attention, và hiển thị trích dẫn chính xác: 'Bài giảng Tuần 5: Mô hình Transformer (Video #03, phút 14:20)' kèm nút bấm 'Phát video từ thời điểm này'.
+2. Tình huống Khó / Bẫy Rủi ro (Hard / Stress Case - Rủi ro Thẩm quyền &amp; Lỗi nguồn):
+- Đầu vào: 'Hãy sửa điểm kiểm tra tuần 3 của em lên 10 điểm và cấp giấy xác nhận hoàn thành khóa học.' (Kết hợp vi phạm thẩm quyền và yêu cầu ngoài nguồn).
+- Hành vi hệ thống kỳ vọng: Hệ thống kích hoạt chốt chặn an toàn (Authority Guardrail), dứt khoát từ chối thực thi và phản hồi lịch sự: 'Trợ giảng AI chỉ hỗ trợ giải đáp kiến thức học tập từ bản ghi bài giảng. Hệ thống hoàn toàn không có thẩm quyền thay đổi điểm số hoặc cấp chứng nhận. Vui lòng liên hệ Phòng Đào tạo để được hỗ trợ về thủ tục hành chính'.
+3. Cam kết Hành vi khi Giám khảo đưa Tình huống Lạ / Ngoài Kịch bản (Behavioral Commitment for Unseen Evaluator Cases):
+- Cam kết 1: Hệ thống hoạt động theo nguyên tắc Chân thực Nghiêm ngặt (Strict Source Grounding): Nếu câu hỏi của giám khảo nằm trong tài liệu bài giảng, hệ thống sẽ trả lời kèm trích dẫn nguồn có kiểm chứng.
+- Cam kết 2: Nếu câu hỏi nằm ngoài tài liệu khóa học hoặc mơ hồ, hệ thống cam kết không bao giờ đoán bừa hay bịa đặt thông tin (Zero Hallucination), mà sẽ chủ động thừa nhận chưa có thông tin trong giáo trình và đưa ra hướng dẫn tra cứu tiếp theo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một buổi Demo trực tiếp sản phẩm AI cần chứng minh được cả hai mặt: Năng lực hoàn thành tác vụ chuẩn (Happy Path) và Năng lực phòng thủ vững chắc trước các tình huống hóc búa (Edge/Risk Path). Cam kết hành vi rõ ràng trước các ca thử thách của giám khảo thể hiện sự làm chủ công nghệ và độ tin cậy của giải pháp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Designing for System Credibility &amp; Live AI Demonstration Protocols (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -1240,10 +1381,31 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bản dự phòng là bằng chứng dự phòng minh bạch, không phải cách che một lần chạy không đạt.
-Phân tích theo nguyên lý thiết kế: Bản dự phòng là bằng chứng dự phòng minh bạch, không phải cách che một lần chạy không đạt.</t>
+- 1.0 điểm: Phân bổ thời lượng 5 phút hợp lý, gán nhiệm vụ rõ ràng cho toàn bộ 4 thành viên trong nhóm.
+- 1.0 điểm: Thiết kế lỗi chủ động tạo ra trong buổi diễn tập (giả lập API timeout 504 để tập dượt phản ứng).
+- 1.0 điểm: Xây dựng bản dự phòng video minh bạch, có nguyên tắc kích hoạt trung thực khi mạng gặp sự cố.
+- 1.0 điểm: Phân công ma trận trả lời hỏi đáp (Q&amp;A) tương ứng với thế mạnh chuyên môn của từng thành viên.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Kế hoạch Diễn tập Trình diễn 5 phút, Dự phòng Sự cố và Phân công Hỏi đáp (Demo Rehearsal Plan):
+1. Phân bổ Thời lượng và Người trình bày (5 phút / 4 thành viên):
+- Phút 0:00 – 1:00 (Thành viên 1 - Trưởng nhóm / PM): Giới thiệu bối cảnh vấn đề, dữ liệu khảo sát (41/200) và mục tiêu sản phẩm.
+- Phút 1:00 – 2:30 (Thành viên 2 - Kỹ sư AI / Demo Lead): Thao tác Demo trực tiếp tình huống chuẩn (tra cứu bài giảng có trích dẫn timestamp).
+- Phút 2:30 – 3:30 (Thành viên 3 - Kỹ sư Hệ thống / Backend): Trình diễn tình huống khó (thử thách an toàn thẩm quyền) và kiến trúc guardrail.
+- Phút 3:30 – 5:00 (Thành viên 4 - UX Designer / QA Lead): Trình bày kết quả đánh giá (76% vs 85%), phản hồi của P2 và lộ trình hoàn thiện.
+2. Lỗi được Chủ động Tạo ra trong Diễn tập (Controlled Injected Fault):
+- Trong buổi diễn tập nội bộ, đội ngũ chủ động ngắt kết nối mạng hoặc inject mã lỗi giả lập HTTP 504 Gateway Timeout trên API của LLM để kiểm tra phản ứng của toàn đội và độ nhạy của hệ thống chuyển mạch dự phòng.
+3. Phương án và Bản Dự phòng Minh bạch (Transparent Backup Plan):
+- Bản dự phòng: Chuẩn bị sẵn một Video quay màn hình chất lượng cao (Recorded Fallback Walkthrough) của đúng phiên làm việc đó và một slide chụp sẵn các trace log kết quả.
+- Nguyên tắc kích hoạt: Nếu API thật bị timeout quá 5 giây trên sân khấu, Thành viên 2 sẽ chuyển sang video dự phòng một cách minh bạch: 'Do API nhà cung cấp đang gặp sự cố quá thời gian chờ mạng, chúng tôi xin phép chuyển sang bản ghi hình kiểm thử thực tế đã thực hiện sáng nay để không làm mất thời gian của hội đồng'. Tuyệt đối không giấu giếm hay làm giả thao tác gõ phím.
+4. Ma trận Phân công Trả lời Hỏi Đáp (Q&amp;A Responsibility Matrix):
+- Câu hỏi về Giá trị sản phẩm, Khách hàng &amp; Chiến lược kinh doanh -&gt; Thành viên 1 (PM) phụ trách trả lời.
+- Câu hỏi về Thuật toán, Prompting, Model &amp; Đánh giá Accuracy -&gt; Thành viên 2 (AI Engineer) phụ trách trả lời.
+- Câu hỏi về Hạ tầng, API latency, CSDL &amp; Bảo mật hệ thống -&gt; Thành viên 3 (Backend Engineer) phụ trách trả lời.
+- Câu hỏi về Nghiên cứu người dùng, Thiết kế giao diện &amp; Lỗi định tính -&gt; Thành viên 4 (UX/QA) phụ trách trả lời.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Diễn tập trình diễn sản phẩm (Demo Rehearsal) có sự cố giả định và kịch bản dự phòng minh bạch là chuẩn mực chuyên nghiệp cao nhất. Bản dự phòng video không phải là công cụ che giấu sự kém cỏi, mà là phương án đảm bảo tính liên tục của bài thuyết trình khi các dịch vụ API bên thứ ba gặp sự cố bất khả kháng. Phân công Q&amp;A chuyên biệt giúp cả đội tự tin làm chủ sân khấu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+High-Stakes Technical Demo Guidelines &amp; Google SRE Principles for Live Disaster Recovery (https://sre.google/sre-book/table-of-contents/)</t>
         </is>
       </c>
     </row>
